--- a/output/pdf_financials_xlsx/ULTA.xlsx
+++ b/output/pdf_financials_xlsx/ULTA.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001748</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.053274</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.052751</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001748</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.053274</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.052751</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.200045</v>
+        <v>0.198297</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.138661</v>
+        <v>0.085387</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.138759</v>
+        <v>0.086008</v>
       </c>
     </row>
     <row r="49">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">

--- a/output/pdf_financials_xlsx/ULTA.xlsx
+++ b/output/pdf_financials_xlsx/ULTA.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.134713</v>
+        <v>0.236813</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.166524</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.127515</v>
+        <v>0.131215</v>
       </c>
     </row>
     <row r="8">
@@ -748,14 +748,20 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.454218</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-0.389448</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>-0.266632</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -765,13 +771,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.466707</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.00027</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.000272</v>
       </c>
     </row>
     <row r="22">
@@ -895,7 +901,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.057504</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -911,7 +917,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.454218</v>
+        <v>-0.396714</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.389448</v>
@@ -1480,13 +1486,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.247704</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.386701</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.422116</v>
       </c>
     </row>
     <row r="65">
@@ -1528,13 +1534,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.048658</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.050779</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.074739</v>
       </c>
     </row>
     <row r="68">
@@ -2059,7 +2065,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.057504</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2075,13 +2081,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001868</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.11064</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000811</v>
       </c>
     </row>
     <row r="102">
@@ -2155,13 +2161,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.097243</v>
+        <v>0.095375</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.141118</v>
+        <v>0.251758</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.059458</v>
+        <v>0.058647</v>
       </c>
     </row>
     <row r="107">
@@ -3652,7 +3658,11 @@
           <t>Net loss for the continuing operations</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.466707</v>
       </c>
@@ -3797,7 +3807,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -3855,7 +3869,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.001868</v>
       </c>
@@ -4432,7 +4450,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.057504</v>
       </c>
@@ -4781,7 +4803,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -5093,7 +5119,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -5122,7 +5152,11 @@
           <t>Net loss from discontinued operation (Note 16)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -5478,7 +5512,11 @@
           <t>Directors’ fees (Note 10)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.1021</v>
       </c>
@@ -5765,7 +5803,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>-0.466707</v>
       </c>
@@ -5794,7 +5836,11 @@
           <t>Net gain (loss) from discontinued operation (Note 17)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.012489</v>
       </c>
